--- a/MODELL_UEBERSICHT.xlsx
+++ b/MODELL_UEBERSICHT.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -3050,6 +3050,582 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>260316/21-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>20260311_1435_NEps1000_RobOpac5_NPrim6_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260311_1435_NEps1000_RobOpac5_NPrim6_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3</v>
+      </c>
+      <c r="K28" t="n">
+        <v>10</v>
+      </c>
+      <c r="L28" t="n">
+        <v>10</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P28" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>o06jzk7i</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>260317/01-09</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>20260312_1002_NEps1000_RobOpac10_NPrim14_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260312_1002_NEps1000_RobOpac10_NPrim14_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>100</v>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>10</v>
+      </c>
+      <c r="L29" t="n">
+        <v>10</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P29" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>6yrwqidu</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>260317/09-10</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>20260312_1645_NEps1000_RobOpac10_NPrim16_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260312_1645_NEps1000_RobOpac10_NPrim16_NCams1_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>10</v>
+      </c>
+      <c r="L30" t="n">
+        <v>10</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P30" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>9tm3smww</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>260318/00-08</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>20260317_1512_NEps1000_RobOpac10_NPrim14_NCams2_FuseSbS_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260317_1512_NEps1000_RobOpac10_NPrim14_NCams2_FuseSbS_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>100</v>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" t="n">
+        <v>10</v>
+      </c>
+      <c r="L31" t="n">
+        <v>10</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P31" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>SbS</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>8xgbcrrt</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>260318/09-22</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>20260318_0012_NEps1000_RobOpac10_NPrim14_NCams2_FuseSbS_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260318_0012_NEps1000_RobOpac10_NPrim14_NCams2_FuseSbS_NCube1_EEFfix_TrackGrip_SterileBg</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P32" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>SbS</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>06muq9kn</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>260318/21-38</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>20260318_1434_NEps1000_RobOpac10_NPrim14_NCams1_NCube1_EEFfix_TrackGrip_SterileBg_BigObject</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>/media/tsp_jw/data/DINO_WM/fcs_datasets/20260318_1434_NEps1000_RobOpac10_NPrim14_NCams1_NCube1_EEFfix_TrackGrip_SterileBg_BigObject</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>100</v>
+      </c>
+      <c r="E33" t="n">
+        <v>4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>10</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="P33" t="n">
+        <v>224</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>EEFfix, TrackGrip, SterileBg</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>tanjv4tq</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
